--- a/src/Proyectos/PP22121-01/Rev_R0/FactorK_48/Espesor_0.060/PP22121-01-(16ga ANSI-61) - K48 - V0-R0.xlsx
+++ b/src/Proyectos/PP22121-01/Rev_R0/FactorK_48/Espesor_0.060/PP22121-01-(16ga ANSI-61) - K48 - V0-R0.xlsx
@@ -217,16 +217,6 @@
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
 <headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{FC69A8AF-5D4E-4C8A-B81E-5152643D316B}" diskRevisions="1" revisionId="159" version="3">
-  <header guid="{7E2E05D5-A730-4F67-A63C-428F164B734A}" dateTime="2026-06-08T10:59:50" maxSheetId="2" userName="Estacion Maquinados" r:id="rId1">
-    <sheetIdMap count="1">
-      <sheetId val="1"/>
-    </sheetIdMap>
-  </header>
-  <header guid="{02E6F0AD-507E-47AA-8561-3A62F0867EF1}" dateTime="2026-06-08T13:31:17" maxSheetId="2" userName="Estacion Maquinados" r:id="rId2" minRId="1" maxRId="94">
-    <sheetIdMap count="1">
-      <sheetId val="1"/>
-    </sheetIdMap>
-  </header>
   <header guid="{FC69A8AF-5D4E-4C8A-B81E-5152643D316B}" dateTime="2026-06-22T12:00:45" maxSheetId="3" userName="Estacion Maquinados" r:id="rId3" minRId="95" maxRId="159">
     <sheetIdMap count="2">
       <sheetId val="1"/>
@@ -234,1843 +224,6 @@
     </sheetIdMap>
   </header>
 </headers>
-</file>
-
-<file path=xl/revisions/revisionLog1.xml><?xml version="1.0" encoding="utf-8"?>
-<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac"/>
-</file>
-
-<file path=xl/revisions/revisionLog2.xml><?xml version="1.0" encoding="utf-8"?>
-<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <rcc rId="1" sId="1">
-    <nc r="A2" t="inlineStr">
-      <is>
-        <t>A</t>
-      </is>
-    </nc>
-  </rcc>
-  <rcc rId="2" sId="1">
-    <nc r="A3" t="inlineStr">
-      <is>
-        <t>B</t>
-      </is>
-    </nc>
-  </rcc>
-  <rrc rId="3" sId="1" eol="1" ref="A4:XFD4" action="insertRow"/>
-  <rcc rId="4" sId="1">
-    <nc r="A4" t="inlineStr">
-      <is>
-        <t>C</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A4">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="5" sId="1" eol="1" ref="A5:XFD5" action="insertRow"/>
-  <rcc rId="6" sId="1">
-    <nc r="A5" t="inlineStr">
-      <is>
-        <t>D</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A5">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="7" sId="1" eol="1" ref="A6:XFD6" action="insertRow"/>
-  <rcc rId="8" sId="1">
-    <nc r="A6" t="inlineStr">
-      <is>
-        <t>E</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A6">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="9" sId="1" eol="1" ref="A7:XFD7" action="insertRow"/>
-  <rcc rId="10" sId="1">
-    <nc r="A7" t="inlineStr">
-      <is>
-        <t>F</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A7">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="11" sId="1" eol="1" ref="A8:XFD8" action="insertRow"/>
-  <rcc rId="12" sId="1">
-    <nc r="A8" t="inlineStr">
-      <is>
-        <t>G</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A8">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="13" sId="1" eol="1" ref="A9:XFD9" action="insertRow"/>
-  <rcc rId="14" sId="1">
-    <nc r="A9" t="inlineStr">
-      <is>
-        <t>H</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A9">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="15" sId="1" eol="1" ref="A10:XFD10" action="insertRow"/>
-  <rcc rId="16" sId="1">
-    <nc r="A10" t="inlineStr">
-      <is>
-        <t>I</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A10">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="17" sId="1" eol="1" ref="A11:XFD11" action="insertRow"/>
-  <rcc rId="18" sId="1">
-    <nc r="A11" t="inlineStr">
-      <is>
-        <t>J</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A11">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="19" sId="1" eol="1" ref="A12:XFD12" action="insertRow"/>
-  <rcc rId="20" sId="1">
-    <nc r="A12" t="inlineStr">
-      <is>
-        <t>K</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A12">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="21" sId="1" eol="1" ref="A13:XFD13" action="insertRow"/>
-  <rcc rId="22" sId="1">
-    <nc r="A13" t="inlineStr">
-      <is>
-        <t>L</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A13">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="23" sId="1" eol="1" ref="A14:XFD14" action="insertRow"/>
-  <rfmt sheetId="1" sqref="A14">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rcc rId="24" sId="1">
-    <nc r="A14" t="inlineStr">
-      <is>
-        <t>M</t>
-      </is>
-    </nc>
-  </rcc>
-  <rrc rId="25" sId="1" eol="1" ref="A15:XFD15" action="insertRow"/>
-  <rcc rId="26" sId="1">
-    <nc r="A15" t="inlineStr">
-      <is>
-        <t>N</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A15">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="27" sId="1" eol="1" ref="A16:XFD16" action="insertRow"/>
-  <rcc rId="28" sId="1">
-    <nc r="A16" t="inlineStr">
-      <is>
-        <t>Ñ</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A16">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="29" sId="1" eol="1" ref="A17:XFD17" action="insertRow"/>
-  <rcc rId="30" sId="1">
-    <nc r="A17" t="inlineStr">
-      <is>
-        <t>O</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A17">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="31" sId="1" eol="1" ref="A18:XFD18" action="insertRow"/>
-  <rcc rId="32" sId="1">
-    <nc r="A18" t="inlineStr">
-      <is>
-        <t>P</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A18">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="33" sId="1" eol="1" ref="A19:XFD19" action="insertRow"/>
-  <rcc rId="34" sId="1">
-    <nc r="A19" t="inlineStr">
-      <is>
-        <t>Q</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A19">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="35" sId="1" eol="1" ref="A20:XFD20" action="insertRow"/>
-  <rcc rId="36" sId="1">
-    <nc r="A20" t="inlineStr">
-      <is>
-        <t>R</t>
-      </is>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="A20">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rrc rId="37" sId="1" eol="1" ref="A21:XFD21" action="insertRow"/>
-  <rfmt sheetId="1" sqref="A21">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </rfmt>
-  <rcc rId="38" sId="1">
-    <nc r="B2">
-      <v>0.38</v>
-    </nc>
-  </rcc>
-  <rfmt sheetId="1" sqref="B2:B21">
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-  </rfmt>
-  <rcc rId="39" sId="1" numFmtId="4">
-    <nc r="B3">
-      <v>6.23</v>
-    </nc>
-  </rcc>
-  <rcc rId="40" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B4">
-      <v>1.38</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="41" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B5">
-      <v>1</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="42" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B6">
-      <v>10.029999999999999</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="43" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B7">
-      <v>9.5</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="44" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B8">
-      <v>0.38</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="45" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B9">
-      <v>6.23</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="46" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B10">
-      <v>17.88</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="47" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B11">
-      <v>0.11</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="48" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B12">
-      <v>0.63</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="49" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B13">
-      <v>1.63</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="50" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B14">
-      <v>0.19</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="51" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B15">
-      <v>0.88</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="52" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B16">
-      <v>19</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="53" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B17">
-      <v>24.97</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="54" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B18">
-      <v>0.63</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="55" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B19">
-      <v>0.12</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="56" sId="1" odxf="1" dxf="1" numFmtId="4">
-    <nc r="B20">
-      <v>0.25</v>
-    </nc>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="57" sId="1" odxf="1" dxf="1">
-    <nc r="C2">
-      <f>B2-0.015</f>
-    </nc>
-    <odxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </odxf>
-    <ndxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="58" sId="1" odxf="1" dxf="1">
-    <nc r="D2">
-      <f>B2+0.015</f>
-    </nc>
-    <odxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </odxf>
-    <ndxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="59" sId="1" odxf="1" dxf="1">
-    <nc r="C3">
-      <f>B3-0.015</f>
-    </nc>
-    <odxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </odxf>
-    <ndxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="60" sId="1" odxf="1" dxf="1">
-    <nc r="C4">
-      <f>B4-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="61" sId="1" odxf="1" dxf="1">
-    <nc r="C5">
-      <f>B5-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="62" sId="1" odxf="1" dxf="1">
-    <nc r="C6">
-      <f>B6-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="63" sId="1" odxf="1" dxf="1">
-    <nc r="C7">
-      <f>B7-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="64" sId="1" odxf="1" dxf="1">
-    <nc r="C8">
-      <f>B8-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="65" sId="1" odxf="1" dxf="1">
-    <nc r="C9">
-      <f>B9-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="66" sId="1" odxf="1" dxf="1">
-    <nc r="C10">
-      <f>B10-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="67" sId="1" odxf="1" dxf="1">
-    <nc r="C11">
-      <f>B11-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="68" sId="1" odxf="1" dxf="1">
-    <nc r="C12">
-      <f>B12-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="69" sId="1" odxf="1" dxf="1">
-    <nc r="C13">
-      <f>B13-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="70" sId="1" odxf="1" dxf="1">
-    <nc r="C14">
-      <f>B14-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="71" sId="1" odxf="1" dxf="1">
-    <nc r="C15">
-      <f>B15-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="72" sId="1" odxf="1" dxf="1">
-    <nc r="C16">
-      <f>B16-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="73" sId="1" odxf="1" dxf="1">
-    <nc r="C17">
-      <f>B17-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="74" sId="1" odxf="1" dxf="1">
-    <nc r="C18">
-      <f>B18-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="75" sId="1" odxf="1" dxf="1">
-    <nc r="C19">
-      <f>B19-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="76" sId="1" odxf="1" dxf="1">
-    <nc r="C20">
-      <f>B20-0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="77" sId="1" odxf="1" dxf="1">
-    <nc r="D3">
-      <f>B3+0.015</f>
-    </nc>
-    <odxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </odxf>
-    <ndxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="78" sId="1" odxf="1" dxf="1">
-    <nc r="D4">
-      <f>B4+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="79" sId="1" odxf="1" dxf="1">
-    <nc r="D5">
-      <f>B5+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="80" sId="1" odxf="1" dxf="1">
-    <nc r="D6">
-      <f>B6+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="81" sId="1" odxf="1" dxf="1">
-    <nc r="D7">
-      <f>B7+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="82" sId="1" odxf="1" dxf="1">
-    <nc r="D8">
-      <f>B8+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="83" sId="1" odxf="1" dxf="1">
-    <nc r="D9">
-      <f>B9+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="84" sId="1" odxf="1" dxf="1">
-    <nc r="D10">
-      <f>B10+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="85" sId="1" odxf="1" dxf="1">
-    <nc r="D11">
-      <f>B11+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="86" sId="1" odxf="1" dxf="1">
-    <nc r="D12">
-      <f>B12+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="87" sId="1" odxf="1" dxf="1">
-    <nc r="D13">
-      <f>B13+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="88" sId="1" odxf="1" dxf="1">
-    <nc r="D14">
-      <f>B14+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="89" sId="1" odxf="1" dxf="1">
-    <nc r="D15">
-      <f>B15+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="90" sId="1" odxf="1" dxf="1">
-    <nc r="D16">
-      <f>B16+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="91" sId="1" odxf="1" dxf="1">
-    <nc r="D17">
-      <f>B17+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="92" sId="1" odxf="1" dxf="1">
-    <nc r="D18">
-      <f>B18+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="93" sId="1" odxf="1" dxf="1">
-    <nc r="D19">
-      <f>B19+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rcc rId="94" sId="1" odxf="1" dxf="1">
-    <nc r="D20">
-      <f>B20+0.015</f>
-    </nc>
-    <odxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </odxf>
-    <ndxf>
-      <font>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Century Gothic"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </ndxf>
-  </rcc>
-  <rfmt sheetId="1" sqref="A1:H20" start="0" length="2147483647">
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-  </rfmt>
-  <rfmt sheetId="1" sqref="A1:A20" start="0" length="0">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-  </rfmt>
-  <rfmt sheetId="1" sqref="A1:H1" start="0" length="0">
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-  </rfmt>
-  <rfmt sheetId="1" sqref="H1:H20" start="0" length="0">
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-  </rfmt>
-  <rfmt sheetId="1" sqref="A20:H20" start="0" length="0">
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-  </rfmt>
-  <rfmt sheetId="1" sqref="A1:H20">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-  </rfmt>
-</revisions>
 </file>
 
 <file path=xl/revisions/revisionLog3.xml><?xml version="1.0" encoding="utf-8"?>
